--- a/data/trans_dic/P57_AC_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,89; 70,48</t>
+          <t>61,79; 70,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,26; 68,03</t>
+          <t>58,21; 68,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,62; 79,68</t>
+          <t>71,67; 80,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,65; 59,97</t>
+          <t>50,96; 60,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,89; 70,93</t>
+          <t>59,73; 71,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,67; 72,98</t>
+          <t>61,19; 72,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,52; 81,64</t>
+          <t>72,4; 81,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,04; 55,18</t>
+          <t>46,8; 55,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,31; 69,33</t>
+          <t>62,13; 69,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,32; 68,88</t>
+          <t>61,15; 68,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,65; 80,08</t>
+          <t>73,59; 79,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,52; 56,47</t>
+          <t>50,51; 56,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,42; 66,98</t>
+          <t>56,4; 66,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,91; 70,4</t>
+          <t>60,35; 70,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,84; 78,95</t>
+          <t>69,85; 78,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,18; 67,99</t>
+          <t>58,52; 68,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,16; 70,56</t>
+          <t>60,86; 70,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,6; 75,6</t>
+          <t>64,98; 75,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,87; 81,84</t>
+          <t>73,59; 82,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,2; 67,49</t>
+          <t>59,23; 67,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,44; 67,42</t>
+          <t>60,19; 67,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,08; 71,11</t>
+          <t>64,11; 71,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,68; 78,91</t>
+          <t>72,59; 79,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,13; 66,59</t>
+          <t>60,14; 66,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,37; 75,2</t>
+          <t>67,47; 75,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,68; 69,57</t>
+          <t>62,23; 69,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,53; 87,07</t>
+          <t>80,71; 87,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 64,07</t>
+          <t>16,61; 65,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,18; 76,3</t>
+          <t>62,74; 76,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 75,24</t>
+          <t>63,86; 75,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,3; 90,94</t>
+          <t>79,47; 90,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,97; 71,69</t>
+          <t>59,3; 71,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,01; 75,05</t>
+          <t>67,88; 74,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,3; 69,94</t>
+          <t>63,59; 69,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81,83; 87,18</t>
+          <t>81,59; 87,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,44; 64,83</t>
+          <t>18,04; 64,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,15; 73,29</t>
+          <t>67,89; 72,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,96; 70,61</t>
+          <t>65,3; 70,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,76; 81,45</t>
+          <t>76,75; 81,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,54; 67,35</t>
+          <t>60,67; 66,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,86; 76,5</t>
+          <t>69,48; 76,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,56; 80,83</t>
+          <t>74,47; 80,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,63; 85,98</t>
+          <t>80,69; 85,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,62; 64,85</t>
+          <t>58,66; 64,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,45; 73,46</t>
+          <t>69,57; 73,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,67; 74,0</t>
+          <t>69,64; 73,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,99; 82,8</t>
+          <t>79,03; 82,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,82; 65,36</t>
+          <t>60,6; 65,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,88; 75,74</t>
+          <t>65,81; 75,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,48; 74,78</t>
+          <t>66,18; 74,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,01; 83,75</t>
+          <t>77,51; 84,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,36; 72,74</t>
+          <t>63,49; 73,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,96; 80,8</t>
+          <t>73,9; 80,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,92; 79,0</t>
+          <t>72,49; 79,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,11; 87,33</t>
+          <t>82,24; 87,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,19; 69,6</t>
+          <t>46,49; 69,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72,07; 77,87</t>
+          <t>72,14; 77,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,49; 76,38</t>
+          <t>71,07; 76,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80,84; 84,98</t>
+          <t>80,72; 84,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,42; 68,9</t>
+          <t>51,96; 69,05</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50,87; 62,04</t>
+          <t>50,99; 61,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,59; 65,48</t>
+          <t>53,71; 65,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,81; 81,84</t>
+          <t>71,71; 81,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,1; 52,31</t>
+          <t>31,64; 53,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,51; 71,7</t>
+          <t>66,59; 71,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,64; 73,97</t>
+          <t>68,5; 74,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,47; 84,0</t>
+          <t>78,89; 83,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,95; 66,97</t>
+          <t>59,91; 66,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64,34; 68,98</t>
+          <t>64,09; 69,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,57; 71,63</t>
+          <t>66,32; 71,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78,24; 82,69</t>
+          <t>78,25; 82,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,87; 61,55</t>
+          <t>53,93; 61,58</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,44; 69,7</t>
+          <t>66,24; 69,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,79; 68,07</t>
+          <t>64,89; 68,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,54; 80,48</t>
+          <t>77,63; 80,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,09; 61,75</t>
+          <t>43,71; 61,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,16; 72,23</t>
+          <t>69,12; 72,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,62; 74,66</t>
+          <t>71,55; 74,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,77; 83,45</t>
+          <t>80,88; 83,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57,02; 63,26</t>
+          <t>55,86; 63,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68,24; 70,6</t>
+          <t>68,19; 70,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68,79; 70,94</t>
+          <t>68,75; 71,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,67; 81,54</t>
+          <t>79,61; 81,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,07; 62,01</t>
+          <t>51,48; 61,86</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>292557; 333130</t>
+          <t>292090; 335037</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>254129; 296731</t>
+          <t>253895; 296733</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306717; 341218</t>
+          <t>306896; 344199</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252868; 299406</t>
+          <t>254422; 301378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182969; 216718</t>
+          <t>182504; 217177</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>191944; 227156</t>
+          <t>190431; 226635</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>250244; 281714</t>
+          <t>249853; 282294</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>208890; 245035</t>
+          <t>207848; 244993</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>484876; 539565</t>
+          <t>483494; 539045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>458311; 514791</t>
+          <t>457014; 513394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>569517; 619250</t>
+          <t>569074; 617213</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>476582; 532724</t>
+          <t>476458; 537054</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>206133; 244746</t>
+          <t>206075; 244730</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>253853; 293386</t>
+          <t>251538; 293779</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>260588; 294544</t>
+          <t>260613; 294364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>262087; 306299</t>
+          <t>263629; 307749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>227423; 262392</t>
+          <t>226313; 262971</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>215992; 252755</t>
+          <t>217247; 252319</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>269849; 303072</t>
+          <t>272515; 304922</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>225197; 256740</t>
+          <t>225339; 257884</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>445597; 497031</t>
+          <t>443766; 497618</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>481331; 534097</t>
+          <t>481551; 536009</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>540273; 586653</t>
+          <t>539611; 587639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>499626; 553310</t>
+          <t>499713; 550906</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>365391; 407875</t>
+          <t>365931; 408983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>384715; 433932</t>
+          <t>388124; 435708</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>419501; 453568</t>
+          <t>420441; 454563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90700; 425530</t>
+          <t>110307; 432057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103718; 127266</t>
+          <t>104653; 127601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>165224; 195027</t>
+          <t>165518; 194910</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128926; 147854</t>
+          <t>129202; 147939</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98693; 117974</t>
+          <t>97597; 117807</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>482327; 532235</t>
+          <t>481413; 531041</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>558900; 617471</t>
+          <t>561434; 617736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>559312; 595923</t>
+          <t>557726; 596096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>169397; 537273</t>
+          <t>149498; 536632</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>843898; 907626</t>
+          <t>840661; 903540</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>746432; 811417</t>
+          <t>750355; 814090</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>877699; 931316</t>
+          <t>877575; 931540</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>622754; 692834</t>
+          <t>624137; 689030</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>499023; 546446</t>
+          <t>496298; 545499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>569421; 617281</t>
+          <t>568722; 616347</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>662944; 706882</t>
+          <t>663451; 705770</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>447056; 494627</t>
+          <t>447381; 495231</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1356115; 1434396</t>
+          <t>1358447; 1440274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1332695; 1415420</t>
+          <t>1332078; 1410372</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1552624; 1627439</t>
+          <t>1553431; 1622183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1089593; 1170957</t>
+          <t>1085629; 1172638</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>230935; 265504</t>
+          <t>230694; 265166</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>334666; 376414</t>
+          <t>333162; 374798</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473981; 515484</t>
+          <t>477104; 517593</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>296487; 340355</t>
+          <t>297094; 342294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>420650; 459570</t>
+          <t>420331; 459754</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>552978; 599023</t>
+          <t>549663; 599999</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>602007; 640260</t>
+          <t>602963; 640396</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>375352; 578118</t>
+          <t>386130; 579877</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>662563; 715891</t>
+          <t>663184; 716066</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>901967; 963695</t>
+          <t>896686; 960527</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1090220; 1146094</t>
+          <t>1088586; 1143133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>680694; 894682</t>
+          <t>674803; 896659</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>151688; 184993</t>
+          <t>152062; 184642</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142005; 173521</t>
+          <t>142334; 174258</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>203333; 234988</t>
+          <t>205925; 234289</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74282; 124932</t>
+          <t>75565; 126715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>830593; 895403</t>
+          <t>831534; 894204</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>757929; 816866</t>
+          <t>756422; 819600</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>854617; 903346</t>
+          <t>848386; 899305</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>446555; 498833</t>
+          <t>446221; 497816</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>995265; 1067091</t>
+          <t>991449; 1067722</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>911554; 980771</t>
+          <t>908097; 980999</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1066023; 1126663</t>
+          <t>1066170; 1128338</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>529930; 605419</t>
+          <t>530515; 605764</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2171123; 2277494</t>
+          <t>2164272; 2272478</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2198921; 2310314</t>
+          <t>2202311; 2312745</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2611789; 2710941</t>
+          <t>2614751; 2709011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1476817; 2068411</t>
+          <t>1463950; 2067573</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2334801; 2438598</t>
+          <t>2333578; 2437570</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2528920; 2636408</t>
+          <t>2526548; 2641447</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2833875; 2927970</t>
+          <t>2837780; 2927701</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1897158; 2104860</t>
+          <t>1858732; 2105796</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4533373; 4690545</t>
+          <t>4530105; 4685517</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4763928; 4912896</t>
+          <t>4760969; 4926007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5478794; 5607625</t>
+          <t>5475051; 5609981</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3476881; 4140151</t>
+          <t>3437115; 4129955</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AC_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,79; 70,88</t>
+          <t>61,29; 70,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,21; 68,03</t>
+          <t>58,26; 68,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,67; 80,38</t>
+          <t>71,74; 80,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,96; 60,36</t>
+          <t>52,3; 60,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,73; 71,08</t>
+          <t>59,46; 70,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,19; 72,82</t>
+          <t>61,81; 73,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,4; 81,81</t>
+          <t>72,19; 81,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,8; 55,17</t>
+          <t>48,06; 56,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,27</t>
+          <t>62,49; 69,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,15; 68,69</t>
+          <t>60,95; 68,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,59; 79,82</t>
+          <t>73,43; 79,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,51; 56,93</t>
+          <t>51,03; 57,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,4; 66,98</t>
+          <t>56,28; 67,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,35; 70,49</t>
+          <t>60,41; 70,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,85; 78,9</t>
+          <t>69,83; 78,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,52; 68,31</t>
+          <t>59,85; 69,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,86; 70,72</t>
+          <t>61,12; 70,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,98; 75,47</t>
+          <t>65,5; 75,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,59; 82,34</t>
+          <t>72,95; 82,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,23; 67,79</t>
+          <t>58,84; 67,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,19; 67,5</t>
+          <t>60,45; 67,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,11; 71,36</t>
+          <t>63,96; 71,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,59; 79,05</t>
+          <t>72,91; 79,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,14; 66,3</t>
+          <t>60,84; 67,26</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,47; 75,4</t>
+          <t>67,77; 75,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,23; 69,86</t>
+          <t>61,98; 69,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,71; 87,26</t>
+          <t>80,49; 86,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 65,06</t>
+          <t>58,17; 66,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,74; 76,5</t>
+          <t>62,73; 76,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,86; 75,2</t>
+          <t>63,06; 75,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,47; 90,99</t>
+          <t>79,19; 90,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,3; 71,58</t>
+          <t>58,33; 70,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,88; 74,88</t>
+          <t>67,85; 74,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,59; 69,97</t>
+          <t>63,59; 69,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81,59; 87,21</t>
+          <t>81,57; 87,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 64,76</t>
+          <t>59,32; 66,72</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,89; 72,96</t>
+          <t>67,93; 73,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,3; 70,85</t>
+          <t>64,77; 70,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,75; 81,47</t>
+          <t>76,75; 81,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,67; 66,98</t>
+          <t>61,57; 68,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,48; 76,37</t>
+          <t>69,8; 76,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,47; 80,71</t>
+          <t>74,67; 80,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,69; 85,84</t>
+          <t>80,7; 85,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,66; 64,93</t>
+          <t>60,57; 66,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,57; 73,76</t>
+          <t>69,48; 73,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,64; 73,73</t>
+          <t>69,43; 73,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,03; 82,53</t>
+          <t>78,85; 82,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,6; 65,46</t>
+          <t>61,93; 66,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,81; 75,64</t>
+          <t>65,54; 75,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,18; 74,46</t>
+          <t>66,67; 75,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,51; 84,09</t>
+          <t>77,31; 83,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,49; 73,15</t>
+          <t>63,84; 72,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,9; 80,84</t>
+          <t>73,62; 80,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,49; 79,12</t>
+          <t>72,52; 78,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,24; 87,35</t>
+          <t>81,89; 87,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,49; 69,81</t>
+          <t>68,41; 73,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72,14; 77,89</t>
+          <t>72,17; 77,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,07; 76,13</t>
+          <t>71,39; 76,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80,72; 84,76</t>
+          <t>80,79; 84,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,96; 69,05</t>
+          <t>67,67; 72,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50,99; 61,92</t>
+          <t>50,94; 62,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,71; 65,76</t>
+          <t>53,86; 66,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,71; 81,59</t>
+          <t>71,49; 81,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,64; 53,05</t>
+          <t>34,66; 54,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,59; 71,61</t>
+          <t>66,43; 71,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,5; 74,22</t>
+          <t>68,91; 74,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,89; 83,62</t>
+          <t>79,01; 83,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,91; 66,84</t>
+          <t>61,04; 67,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64,09; 69,02</t>
+          <t>64,25; 68,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,32; 71,64</t>
+          <t>66,87; 71,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78,25; 82,81</t>
+          <t>78,25; 82,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,93; 61,58</t>
+          <t>56,29; 63,55</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>63,2%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,24; 69,55</t>
+          <t>66,45; 69,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,89; 68,14</t>
+          <t>64,76; 68,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,63; 80,43</t>
+          <t>77,56; 80,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,71; 61,73</t>
+          <t>60,63; 64,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,12; 72,2</t>
+          <t>69,28; 72,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,55; 74,81</t>
+          <t>71,48; 74,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,88; 83,44</t>
+          <t>80,81; 83,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,86; 63,29</t>
+          <t>62,5; 65,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68,19; 70,53</t>
+          <t>68,19; 70,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68,75; 71,13</t>
+          <t>68,64; 70,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,61; 81,58</t>
+          <t>79,56; 81,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,48; 61,86</t>
+          <t>62,04; 64,51</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277391</t>
+          <t>307769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>227310</t>
+          <t>253150</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>504701</t>
+          <t>560919</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>292090; 335037</t>
+          <t>289708; 333903</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>253895; 296733</t>
+          <t>254103; 297889</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306896; 344199</t>
+          <t>307213; 344195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>254422; 301378</t>
+          <t>284821; 331014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182504; 217177</t>
+          <t>181669; 215809</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>190431; 226635</t>
+          <t>192367; 227955</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>249853; 282294</t>
+          <t>249115; 280319</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>207848; 244993</t>
+          <t>232614; 272772</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>483494; 539045</t>
+          <t>486313; 539914</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>457014; 513394</t>
+          <t>455574; 513104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>569074; 617213</t>
+          <t>567849; 615732</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>476458; 537054</t>
+          <t>524949; 590023</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283740</t>
+          <t>310796</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>242866</t>
+          <t>266685</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>526605</t>
+          <t>577481</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>206075; 244730</t>
+          <t>205625; 247097</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>251538; 293779</t>
+          <t>251756; 292426</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>260613; 294364</t>
+          <t>260539; 293793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>263629; 307749</t>
+          <t>288145; 333128</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>226313; 262971</t>
+          <t>227266; 263752</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>217247; 252319</t>
+          <t>218988; 253364</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>272515; 304922</t>
+          <t>270123; 304241</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>225339; 257884</t>
+          <t>247326; 282548</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>443766; 497618</t>
+          <t>445702; 498828</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>481551; 536009</t>
+          <t>480408; 534357</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>539611; 587639</t>
+          <t>542030; 589207</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>499713; 550906</t>
+          <t>548699; 606567</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263501</t>
+          <t>292524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>108019</t>
+          <t>119289</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>371521</t>
+          <t>411812</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>365931; 408983</t>
+          <t>367585; 410313</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>388124; 435708</t>
+          <t>386577; 436155</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>420441; 454563</t>
+          <t>419320; 452920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110307; 432057</t>
+          <t>271163; 312134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>104653; 127601</t>
+          <t>104631; 127431</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>165518; 194910</t>
+          <t>163459; 195529</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>129202; 147939</t>
+          <t>128742; 147710</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97597; 117807</t>
+          <t>107864; 130529</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>481413; 531041</t>
+          <t>481184; 529698</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>561434; 617736</t>
+          <t>561447; 615717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>557726; 596096</t>
+          <t>557529; 596239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>149498; 536632</t>
+          <t>386208; 434418</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>657384</t>
+          <t>728937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>471230</t>
+          <t>538945</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1128615</t>
+          <t>1267882</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>840661; 903540</t>
+          <t>841166; 906501</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>750355; 814090</t>
+          <t>744240; 809555</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>877575; 931540</t>
+          <t>877606; 930115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>624137; 689030</t>
+          <t>692915; 765517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>496298; 545499</t>
+          <t>498584; 545545</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>568722; 616347</t>
+          <t>570228; 617710</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>663451; 705770</t>
+          <t>663527; 705015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>447381; 495231</t>
+          <t>514578; 561238</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1358447; 1440274</t>
+          <t>1356668; 1435639</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1332078; 1410372</t>
+          <t>1328080; 1410447</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1553431; 1622183</t>
+          <t>1549951; 1621318</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1085629; 1172638</t>
+          <t>1223140; 1311702</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319015</t>
+          <t>382876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>509675</t>
+          <t>582024</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>828691</t>
+          <t>964899</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>230694; 265166</t>
+          <t>229754; 265483</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>333162; 374798</t>
+          <t>335585; 378178</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>477104; 517593</t>
+          <t>475860; 514969</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>297094; 342294</t>
+          <t>356695; 405891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>420331; 459754</t>
+          <t>418720; 459728</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>549663; 599999</t>
+          <t>549909; 597247</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>602963; 640396</t>
+          <t>600370; 639692</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>386130; 579877</t>
+          <t>560472; 603933</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>663184; 716066</t>
+          <t>663471; 715096</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>896686; 960527</t>
+          <t>900724; 964791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1088586; 1143133</t>
+          <t>1089568; 1144361</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>674803; 896659</t>
+          <t>932523; 998056</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98622</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>473032</t>
+          <t>535501</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>571654</t>
+          <t>640626</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>152062; 184642</t>
+          <t>151916; 185132</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142334; 174258</t>
+          <t>142715; 175227</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>205925; 234289</t>
+          <t>205282; 234716</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75565; 126715</t>
+          <t>81593; 129097</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>831534; 894204</t>
+          <t>829552; 893734</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>756422; 819600</t>
+          <t>760988; 820729</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>848386; 899305</t>
+          <t>849646; 902658</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>446221; 497816</t>
+          <t>506020; 562724</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>991449; 1067722</t>
+          <t>993950; 1064387</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>908097; 980999</t>
+          <t>915608; 980779</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1066170; 1128338</t>
+          <t>1066235; 1126415</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>530515; 605764</t>
+          <t>599115; 676441</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1899654</t>
+          <t>2128026</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2032133</t>
+          <t>2295593</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3931787</t>
+          <t>4423619</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2164272; 2272478</t>
+          <t>2171362; 2273344</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2202311; 2312745</t>
+          <t>2198023; 2311220</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2614751; 2709011</t>
+          <t>2612585; 2712376</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1463950; 2067573</t>
+          <t>2068625; 2191731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2333578; 2437570</t>
+          <t>2338967; 2442443</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2526548; 2641447</t>
+          <t>2523838; 2635296</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2837780; 2927701</t>
+          <t>2835323; 2922050</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1858732; 2105796</t>
+          <t>2242114; 2346461</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4530105; 4685517</t>
+          <t>4530046; 4681597</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4760969; 4926007</t>
+          <t>4753662; 4913703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5475051; 5609981</t>
+          <t>5471042; 5608386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3437115; 4129955</t>
+          <t>4342249; 4514909</t>
         </is>
       </c>
     </row>
